--- a/Task-2.xlsx
+++ b/Task-2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Excel_Task\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B64C02ED-4184-446D-A90F-60CCEB44F05A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8FACBF3-F217-436A-8956-66ADCEF5E80D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1860,6 +1860,42 @@
     <xf numFmtId="0" fontId="8" fillId="3" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1872,12 +1908,6 @@
     <xf numFmtId="0" fontId="8" fillId="3" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1917,35 +1947,38 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1980,47 +2013,38 @@
     <xf numFmtId="0" fontId="11" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -2034,29 +2058,41 @@
     <xf numFmtId="0" fontId="8" fillId="6" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2083,42 +2119,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -3682,21 +3682,21 @@
       <c r="R2" s="5"/>
     </row>
     <row r="3" spans="1:18" ht="19.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="224" t="s">
+      <c r="A3" s="215" t="s">
         <v>83</v>
       </c>
-      <c r="B3" s="225"/>
-      <c r="C3" s="225"/>
-      <c r="D3" s="225"/>
-      <c r="E3" s="226"/>
+      <c r="B3" s="216"/>
+      <c r="C3" s="216"/>
+      <c r="D3" s="216"/>
+      <c r="E3" s="217"/>
       <c r="F3" s="116"/>
-      <c r="G3" s="218" t="s">
+      <c r="G3" s="230" t="s">
         <v>84</v>
       </c>
-      <c r="H3" s="219"/>
-      <c r="I3" s="219"/>
-      <c r="J3" s="219"/>
-      <c r="K3" s="220"/>
+      <c r="H3" s="231"/>
+      <c r="I3" s="231"/>
+      <c r="J3" s="231"/>
+      <c r="K3" s="232"/>
       <c r="L3" s="101"/>
       <c r="M3" s="5"/>
       <c r="N3" s="5"/>
@@ -3706,21 +3706,21 @@
       <c r="R3" s="5"/>
     </row>
     <row r="4" spans="1:18" ht="19.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="227"/>
-      <c r="B4" s="228"/>
-      <c r="C4" s="228"/>
-      <c r="D4" s="228"/>
-      <c r="E4" s="229"/>
+      <c r="A4" s="218"/>
+      <c r="B4" s="219"/>
+      <c r="C4" s="219"/>
+      <c r="D4" s="219"/>
+      <c r="E4" s="220"/>
       <c r="F4" s="92"/>
-      <c r="G4" s="230" t="s">
+      <c r="G4" s="221" t="s">
         <v>46</v>
       </c>
-      <c r="H4" s="231"/>
-      <c r="I4" s="232"/>
-      <c r="J4" s="230" t="s">
+      <c r="H4" s="222"/>
+      <c r="I4" s="223"/>
+      <c r="J4" s="221" t="s">
         <v>50</v>
       </c>
-      <c r="K4" s="232"/>
+      <c r="K4" s="223"/>
       <c r="L4" s="5"/>
       <c r="M4" s="5"/>
       <c r="N4" s="5"/>
@@ -3733,15 +3733,15 @@
       <c r="B5" s="31"/>
       <c r="E5" s="31"/>
       <c r="F5" s="92"/>
-      <c r="G5" s="233" t="s">
+      <c r="G5" s="224" t="s">
         <v>85</v>
       </c>
-      <c r="H5" s="234"/>
-      <c r="I5" s="235"/>
-      <c r="J5" s="233" t="s">
+      <c r="H5" s="225"/>
+      <c r="I5" s="226"/>
+      <c r="J5" s="224" t="s">
         <v>86</v>
       </c>
-      <c r="K5" s="235"/>
+      <c r="K5" s="226"/>
       <c r="L5" s="5"/>
       <c r="M5" s="5"/>
       <c r="N5" s="5"/>
@@ -3759,15 +3759,15 @@
       <c r="D6" s="102"/>
       <c r="E6" s="118"/>
       <c r="F6" s="92"/>
-      <c r="G6" s="221" t="s">
+      <c r="G6" s="233" t="s">
         <v>87</v>
       </c>
-      <c r="H6" s="222"/>
-      <c r="I6" s="223"/>
-      <c r="J6" s="221" t="s">
+      <c r="H6" s="234"/>
+      <c r="I6" s="235"/>
+      <c r="J6" s="233" t="s">
         <v>88</v>
       </c>
-      <c r="K6" s="223"/>
+      <c r="K6" s="235"/>
       <c r="L6" s="5"/>
       <c r="M6" s="5"/>
       <c r="N6" s="5"/>
@@ -3785,15 +3785,15 @@
       <c r="D7" s="117"/>
       <c r="E7" s="118"/>
       <c r="F7" s="92"/>
-      <c r="G7" s="221" t="s">
+      <c r="G7" s="233" t="s">
         <v>89</v>
       </c>
-      <c r="H7" s="222"/>
-      <c r="I7" s="223"/>
-      <c r="J7" s="221" t="s">
+      <c r="H7" s="234"/>
+      <c r="I7" s="235"/>
+      <c r="J7" s="233" t="s">
         <v>90</v>
       </c>
-      <c r="K7" s="223"/>
+      <c r="K7" s="235"/>
       <c r="L7" s="5"/>
       <c r="M7" s="5"/>
       <c r="N7" s="5"/>
@@ -3809,15 +3809,15 @@
       <c r="D8" s="23"/>
       <c r="E8" s="23"/>
       <c r="F8" s="92"/>
-      <c r="G8" s="221" t="s">
+      <c r="G8" s="233" t="s">
         <v>91</v>
       </c>
-      <c r="H8" s="222"/>
-      <c r="I8" s="223"/>
-      <c r="J8" s="221" t="s">
+      <c r="H8" s="234"/>
+      <c r="I8" s="235"/>
+      <c r="J8" s="233" t="s">
         <v>1</v>
       </c>
-      <c r="K8" s="223"/>
+      <c r="K8" s="235"/>
       <c r="L8" s="5"/>
       <c r="M8" s="5"/>
       <c r="N8" s="5"/>
@@ -3828,15 +3828,15 @@
     </row>
     <row r="9" spans="1:18" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F9" s="92"/>
-      <c r="G9" s="215" t="s">
+      <c r="G9" s="227" t="s">
         <v>92</v>
       </c>
-      <c r="H9" s="216"/>
-      <c r="I9" s="217"/>
-      <c r="J9" s="215" t="s">
+      <c r="H9" s="228"/>
+      <c r="I9" s="229"/>
+      <c r="J9" s="227" t="s">
         <v>93</v>
       </c>
-      <c r="K9" s="217"/>
+      <c r="K9" s="229"/>
       <c r="L9" s="5"/>
       <c r="M9" s="5"/>
       <c r="N9" s="5"/>
@@ -3938,11 +3938,11 @@
         <v>55.600000000000009</v>
       </c>
       <c r="J12" s="111" t="str" cm="1">
-        <f t="array" ref="J12:J34">IF(percent&gt;=80.01,"A+",IF(percent&gt;=60.01,"A",IF(percent&gt;=45.01,"B",IF(percent&gt;=33.01,"B+","C"))))</f>
+        <f t="array" ref="J12:J34">_xlfn.IFS(percent&gt;=80.01,"A+",percent&gt;=60.01,"A",percent&gt;=45.01,"B",percent&gt;=33.01,"B+",percent&lt;33,"C")</f>
         <v>B</v>
       </c>
       <c r="K12" s="111" t="str" cm="1">
-        <f t="array" ref="K12:K34">IF(_xlfn.ANCHORARRAY(J12)="C","Fail","Pass")</f>
+        <f t="array" ref="K12:K34">IF(percent&lt;33,"Fail","Pass")</f>
         <v>Pass</v>
       </c>
       <c r="L12" s="5"/>
@@ -3974,8 +3974,8 @@
         <f t="shared" ref="H13:H34" si="0">SUM(C13:G13)</f>
         <v>266</v>
       </c>
-      <c r="I13" s="112">
-        <f>H13/500*100</f>
+      <c r="I13" s="111">
+        <f t="shared" ref="I13:I34" si="1">H13/500*100</f>
         <v>53.2</v>
       </c>
       <c r="J13" s="112" t="str">
@@ -4013,8 +4013,8 @@
         <f t="shared" si="0"/>
         <v>280</v>
       </c>
-      <c r="I14" s="112">
-        <f t="shared" ref="I14:I34" si="1">H14/500*100</f>
+      <c r="I14" s="111">
+        <f t="shared" si="1"/>
         <v>56.000000000000007</v>
       </c>
       <c r="J14" s="112" t="str">
@@ -4052,7 +4052,7 @@
         <f t="shared" si="0"/>
         <v>359</v>
       </c>
-      <c r="I15" s="112">
+      <c r="I15" s="111">
         <f t="shared" si="1"/>
         <v>71.8</v>
       </c>
@@ -4089,7 +4089,7 @@
         <f t="shared" si="0"/>
         <v>367</v>
       </c>
-      <c r="I16" s="112">
+      <c r="I16" s="111">
         <f t="shared" si="1"/>
         <v>73.400000000000006</v>
       </c>
@@ -4126,7 +4126,7 @@
         <f t="shared" si="0"/>
         <v>245</v>
       </c>
-      <c r="I17" s="112">
+      <c r="I17" s="111">
         <f t="shared" si="1"/>
         <v>49</v>
       </c>
@@ -4163,7 +4163,7 @@
         <f t="shared" si="0"/>
         <v>275</v>
       </c>
-      <c r="I18" s="112">
+      <c r="I18" s="111">
         <f t="shared" si="1"/>
         <v>55.000000000000007</v>
       </c>
@@ -4200,7 +4200,7 @@
         <f t="shared" si="0"/>
         <v>421</v>
       </c>
-      <c r="I19" s="112">
+      <c r="I19" s="111">
         <f t="shared" si="1"/>
         <v>84.2</v>
       </c>
@@ -4237,7 +4237,7 @@
         <f t="shared" si="0"/>
         <v>454</v>
       </c>
-      <c r="I20" s="112">
+      <c r="I20" s="111">
         <f t="shared" si="1"/>
         <v>90.8</v>
       </c>
@@ -4274,7 +4274,7 @@
         <f t="shared" si="0"/>
         <v>282</v>
       </c>
-      <c r="I21" s="112">
+      <c r="I21" s="111">
         <f t="shared" si="1"/>
         <v>56.399999999999991</v>
       </c>
@@ -4311,7 +4311,7 @@
         <f t="shared" si="0"/>
         <v>289</v>
       </c>
-      <c r="I22" s="112">
+      <c r="I22" s="111">
         <f t="shared" si="1"/>
         <v>57.8</v>
       </c>
@@ -4348,7 +4348,7 @@
         <f t="shared" si="0"/>
         <v>234</v>
       </c>
-      <c r="I23" s="112">
+      <c r="I23" s="111">
         <f t="shared" si="1"/>
         <v>46.800000000000004</v>
       </c>
@@ -4385,7 +4385,7 @@
         <f t="shared" si="0"/>
         <v>234</v>
       </c>
-      <c r="I24" s="112">
+      <c r="I24" s="111">
         <f t="shared" si="1"/>
         <v>46.800000000000004</v>
       </c>
@@ -4422,7 +4422,7 @@
         <f t="shared" si="0"/>
         <v>335</v>
       </c>
-      <c r="I25" s="112">
+      <c r="I25" s="111">
         <f t="shared" si="1"/>
         <v>67</v>
       </c>
@@ -4459,7 +4459,7 @@
         <f t="shared" si="0"/>
         <v>220</v>
       </c>
-      <c r="I26" s="112">
+      <c r="I26" s="111">
         <f t="shared" si="1"/>
         <v>44</v>
       </c>
@@ -4496,7 +4496,7 @@
         <f t="shared" si="0"/>
         <v>367</v>
       </c>
-      <c r="I27" s="112">
+      <c r="I27" s="111">
         <f t="shared" si="1"/>
         <v>73.400000000000006</v>
       </c>
@@ -4533,7 +4533,7 @@
         <f t="shared" si="0"/>
         <v>212</v>
       </c>
-      <c r="I28" s="112">
+      <c r="I28" s="111">
         <f t="shared" si="1"/>
         <v>42.4</v>
       </c>
@@ -4577,7 +4577,7 @@
         <f t="shared" si="0"/>
         <v>320</v>
       </c>
-      <c r="I29" s="112">
+      <c r="I29" s="111">
         <f t="shared" si="1"/>
         <v>64</v>
       </c>
@@ -4621,7 +4621,7 @@
         <f t="shared" si="0"/>
         <v>345</v>
       </c>
-      <c r="I30" s="112">
+      <c r="I30" s="111">
         <f t="shared" si="1"/>
         <v>69</v>
       </c>
@@ -4665,7 +4665,7 @@
         <f t="shared" si="0"/>
         <v>346</v>
       </c>
-      <c r="I31" s="112">
+      <c r="I31" s="111">
         <f t="shared" si="1"/>
         <v>69.199999999999989</v>
       </c>
@@ -4709,7 +4709,7 @@
         <f t="shared" si="0"/>
         <v>154</v>
       </c>
-      <c r="I32" s="112">
+      <c r="I32" s="111">
         <f t="shared" si="1"/>
         <v>30.8</v>
       </c>
@@ -4753,7 +4753,7 @@
         <f t="shared" si="0"/>
         <v>151</v>
       </c>
-      <c r="I33" s="112">
+      <c r="I33" s="111">
         <f t="shared" si="1"/>
         <v>30.2</v>
       </c>
@@ -4797,7 +4797,7 @@
         <f t="shared" si="0"/>
         <v>325</v>
       </c>
-      <c r="I34" s="112">
+      <c r="I34" s="111">
         <f t="shared" si="1"/>
         <v>65</v>
       </c>
@@ -4827,11 +4827,6 @@
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="A3:E4"/>
-    <mergeCell ref="G4:I4"/>
-    <mergeCell ref="J4:K4"/>
-    <mergeCell ref="G5:I5"/>
-    <mergeCell ref="J5:K5"/>
     <mergeCell ref="G9:I9"/>
     <mergeCell ref="J9:K9"/>
     <mergeCell ref="G3:K3"/>
@@ -4841,6 +4836,11 @@
     <mergeCell ref="J7:K7"/>
     <mergeCell ref="G8:I8"/>
     <mergeCell ref="J8:K8"/>
+    <mergeCell ref="A3:E4"/>
+    <mergeCell ref="G4:I4"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="G5:I5"/>
+    <mergeCell ref="J5:K5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -9297,16 +9297,16 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:9" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="168" t="s">
+      <c r="A1" s="149" t="s">
         <v>127</v>
       </c>
-      <c r="B1" s="169"/>
-      <c r="C1" s="169"/>
-      <c r="D1" s="169"/>
-      <c r="E1" s="169"/>
-      <c r="F1" s="169"/>
-      <c r="G1" s="169"/>
-      <c r="H1" s="170"/>
+      <c r="B1" s="150"/>
+      <c r="C1" s="150"/>
+      <c r="D1" s="150"/>
+      <c r="E1" s="150"/>
+      <c r="F1" s="150"/>
+      <c r="G1" s="150"/>
+      <c r="H1" s="151"/>
       <c r="I1" s="26"/>
     </row>
     <row r="2" spans="1:9" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -9320,7 +9320,7 @@
       <c r="A3" s="123" t="s">
         <v>128</v>
       </c>
-      <c r="B3" s="171" t="s">
+      <c r="B3" s="152" t="s">
         <v>118</v>
       </c>
       <c r="C3" s="153"/>
@@ -9334,57 +9334,57 @@
       <c r="A4" s="122">
         <v>1</v>
       </c>
-      <c r="B4" s="172" t="s">
+      <c r="B4" s="155" t="s">
         <v>121</v>
       </c>
-      <c r="C4" s="173"/>
-      <c r="D4" s="173"/>
-      <c r="E4" s="173"/>
-      <c r="F4" s="173"/>
-      <c r="G4" s="173"/>
-      <c r="H4" s="174"/>
+      <c r="C4" s="156"/>
+      <c r="D4" s="156"/>
+      <c r="E4" s="156"/>
+      <c r="F4" s="156"/>
+      <c r="G4" s="156"/>
+      <c r="H4" s="157"/>
     </row>
     <row r="5" spans="1:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="A5" s="120">
         <v>2</v>
       </c>
-      <c r="B5" s="172" t="s">
+      <c r="B5" s="155" t="s">
         <v>123</v>
       </c>
-      <c r="C5" s="173"/>
-      <c r="D5" s="173"/>
-      <c r="E5" s="173"/>
-      <c r="F5" s="173"/>
-      <c r="G5" s="173"/>
-      <c r="H5" s="174"/>
+      <c r="C5" s="156"/>
+      <c r="D5" s="156"/>
+      <c r="E5" s="156"/>
+      <c r="F5" s="156"/>
+      <c r="G5" s="156"/>
+      <c r="H5" s="157"/>
       <c r="I5" s="26"/>
     </row>
     <row r="6" spans="1:9" ht="18" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" s="121">
         <v>3</v>
       </c>
-      <c r="B6" s="175" t="s">
+      <c r="B6" s="158" t="s">
         <v>125</v>
       </c>
-      <c r="C6" s="176"/>
-      <c r="D6" s="176"/>
-      <c r="E6" s="176"/>
-      <c r="F6" s="176"/>
-      <c r="G6" s="176"/>
-      <c r="H6" s="177"/>
+      <c r="C6" s="159"/>
+      <c r="D6" s="159"/>
+      <c r="E6" s="159"/>
+      <c r="F6" s="159"/>
+      <c r="G6" s="159"/>
+      <c r="H6" s="160"/>
       <c r="I6" s="26"/>
     </row>
     <row r="7" spans="1:9" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="8" spans="1:9" ht="18.45" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="149" t="s">
+      <c r="A8" s="161" t="s">
         <v>97</v>
       </c>
-      <c r="B8" s="152" t="s">
+      <c r="B8" s="164" t="s">
         <v>119</v>
       </c>
       <c r="C8" s="153"/>
       <c r="D8" s="153"/>
-      <c r="E8" s="152" t="s">
+      <c r="E8" s="164" t="s">
         <v>120</v>
       </c>
       <c r="F8" s="153"/>
@@ -9392,40 +9392,40 @@
       <c r="H8" s="154"/>
     </row>
     <row r="9" spans="1:9" ht="14.55" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="150"/>
-      <c r="B9" s="164" t="s">
+      <c r="A9" s="162"/>
+      <c r="B9" s="174" t="s">
         <v>122</v>
       </c>
-      <c r="C9" s="165"/>
-      <c r="D9" s="166"/>
-      <c r="E9" s="155"/>
-      <c r="F9" s="156"/>
-      <c r="G9" s="156"/>
-      <c r="H9" s="157"/>
+      <c r="C9" s="175"/>
+      <c r="D9" s="176"/>
+      <c r="E9" s="165"/>
+      <c r="F9" s="166"/>
+      <c r="G9" s="166"/>
+      <c r="H9" s="167"/>
     </row>
     <row r="10" spans="1:9" ht="14.55" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="150"/>
-      <c r="B10" s="167" t="s">
+      <c r="A10" s="162"/>
+      <c r="B10" s="177" t="s">
         <v>124</v>
       </c>
-      <c r="C10" s="167"/>
-      <c r="D10" s="167"/>
-      <c r="E10" s="158"/>
-      <c r="F10" s="159"/>
-      <c r="G10" s="159"/>
-      <c r="H10" s="160"/>
+      <c r="C10" s="177"/>
+      <c r="D10" s="177"/>
+      <c r="E10" s="168"/>
+      <c r="F10" s="169"/>
+      <c r="G10" s="169"/>
+      <c r="H10" s="170"/>
     </row>
     <row r="11" spans="1:9" ht="14.55" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="151"/>
-      <c r="B11" s="167" t="s">
+      <c r="A11" s="163"/>
+      <c r="B11" s="177" t="s">
         <v>126</v>
       </c>
-      <c r="C11" s="167"/>
-      <c r="D11" s="167"/>
-      <c r="E11" s="161"/>
-      <c r="F11" s="162"/>
-      <c r="G11" s="162"/>
-      <c r="H11" s="163"/>
+      <c r="C11" s="177"/>
+      <c r="D11" s="177"/>
+      <c r="E11" s="171"/>
+      <c r="F11" s="172"/>
+      <c r="G11" s="172"/>
+      <c r="H11" s="173"/>
       <c r="I11" s="26"/>
     </row>
     <row r="12" spans="1:9" ht="15" thickTop="1" x14ac:dyDescent="0.3">
@@ -9435,11 +9435,6 @@
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="B3:H3"/>
-    <mergeCell ref="B4:H4"/>
-    <mergeCell ref="B5:H5"/>
-    <mergeCell ref="B6:H6"/>
     <mergeCell ref="A8:A11"/>
     <mergeCell ref="E8:H8"/>
     <mergeCell ref="E9:H9"/>
@@ -9449,6 +9444,11 @@
     <mergeCell ref="B9:D9"/>
     <mergeCell ref="B10:D10"/>
     <mergeCell ref="B11:D11"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="B3:H3"/>
+    <mergeCell ref="B4:H4"/>
+    <mergeCell ref="B5:H5"/>
+    <mergeCell ref="B6:H6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -9463,30 +9463,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="22.05" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="178" t="s">
+      <c r="A1" s="189" t="s">
         <v>139</v>
       </c>
-      <c r="B1" s="179"/>
-      <c r="C1" s="179"/>
-      <c r="D1" s="179"/>
-      <c r="E1" s="179"/>
-      <c r="F1" s="179"/>
-      <c r="G1" s="179"/>
-      <c r="H1" s="179"/>
-      <c r="I1" s="179"/>
-      <c r="J1" s="180"/>
+      <c r="B1" s="190"/>
+      <c r="C1" s="190"/>
+      <c r="D1" s="190"/>
+      <c r="E1" s="190"/>
+      <c r="F1" s="190"/>
+      <c r="G1" s="190"/>
+      <c r="H1" s="190"/>
+      <c r="I1" s="190"/>
+      <c r="J1" s="191"/>
     </row>
     <row r="2" spans="1:13" ht="22.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="181"/>
-      <c r="B2" s="182"/>
-      <c r="C2" s="182"/>
-      <c r="D2" s="182"/>
-      <c r="E2" s="182"/>
-      <c r="F2" s="182"/>
-      <c r="G2" s="182"/>
-      <c r="H2" s="182"/>
-      <c r="I2" s="182"/>
-      <c r="J2" s="183"/>
+      <c r="A2" s="192"/>
+      <c r="B2" s="193"/>
+      <c r="C2" s="193"/>
+      <c r="D2" s="193"/>
+      <c r="E2" s="193"/>
+      <c r="F2" s="193"/>
+      <c r="G2" s="193"/>
+      <c r="H2" s="193"/>
+      <c r="I2" s="193"/>
+      <c r="J2" s="194"/>
     </row>
     <row r="3" spans="1:13" s="18" customFormat="1" ht="22.05" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="130"/>
@@ -9502,18 +9502,18 @@
       <c r="K3" s="125"/>
     </row>
     <row r="4" spans="1:13" s="18" customFormat="1" ht="22.05" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="184" t="s">
+      <c r="A4" s="195" t="s">
         <v>97</v>
       </c>
-      <c r="B4" s="184"/>
-      <c r="C4" s="184"/>
-      <c r="D4" s="184"/>
-      <c r="E4" s="184"/>
-      <c r="F4" s="184"/>
-      <c r="G4" s="184"/>
-      <c r="H4" s="184"/>
-      <c r="I4" s="184"/>
-      <c r="J4" s="185"/>
+      <c r="B4" s="195"/>
+      <c r="C4" s="195"/>
+      <c r="D4" s="195"/>
+      <c r="E4" s="195"/>
+      <c r="F4" s="195"/>
+      <c r="G4" s="195"/>
+      <c r="H4" s="195"/>
+      <c r="I4" s="195"/>
+      <c r="J4" s="196"/>
       <c r="K4" s="128"/>
       <c r="M4"/>
     </row>
@@ -9521,16 +9521,16 @@
       <c r="A5" s="124" t="s">
         <v>140</v>
       </c>
-      <c r="B5" s="152" t="s">
+      <c r="B5" s="164" t="s">
         <v>119</v>
       </c>
       <c r="C5" s="153"/>
       <c r="D5" s="154"/>
-      <c r="E5" s="152" t="s">
+      <c r="E5" s="164" t="s">
         <v>138</v>
       </c>
       <c r="F5" s="154"/>
-      <c r="G5" s="152" t="s">
+      <c r="G5" s="164" t="s">
         <v>137</v>
       </c>
       <c r="H5" s="153"/>
@@ -9541,114 +9541,114 @@
       <c r="A6" s="127">
         <v>1</v>
       </c>
-      <c r="B6" s="190" t="s">
+      <c r="B6" s="200" t="s">
         <v>136</v>
       </c>
-      <c r="C6" s="194"/>
-      <c r="D6" s="191"/>
-      <c r="E6" s="190" t="s">
+      <c r="C6" s="202"/>
+      <c r="D6" s="201"/>
+      <c r="E6" s="200" t="s">
         <v>132</v>
       </c>
-      <c r="F6" s="191"/>
-      <c r="G6" s="186"/>
-      <c r="H6" s="187"/>
-      <c r="I6" s="187"/>
-      <c r="J6" s="188"/>
+      <c r="F6" s="201"/>
+      <c r="G6" s="197"/>
+      <c r="H6" s="198"/>
+      <c r="I6" s="198"/>
+      <c r="J6" s="199"/>
       <c r="K6" s="26"/>
     </row>
     <row r="7" spans="1:13" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A7" s="129">
         <v>2</v>
       </c>
-      <c r="B7" s="195" t="s">
+      <c r="B7" s="184" t="s">
         <v>135</v>
       </c>
-      <c r="C7" s="195"/>
-      <c r="D7" s="195"/>
-      <c r="E7" s="192" t="s">
+      <c r="C7" s="184"/>
+      <c r="D7" s="184"/>
+      <c r="E7" s="183" t="s">
         <v>129</v>
       </c>
-      <c r="F7" s="193"/>
-      <c r="G7" s="189"/>
-      <c r="H7" s="189"/>
-      <c r="I7" s="189"/>
-      <c r="J7" s="189"/>
+      <c r="F7" s="185"/>
+      <c r="G7" s="178"/>
+      <c r="H7" s="178"/>
+      <c r="I7" s="178"/>
+      <c r="J7" s="178"/>
       <c r="K7" s="26"/>
     </row>
     <row r="8" spans="1:13" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A8" s="126">
         <v>3</v>
       </c>
-      <c r="B8" s="192" t="s">
+      <c r="B8" s="183" t="s">
         <v>134</v>
       </c>
-      <c r="C8" s="195"/>
-      <c r="D8" s="193"/>
-      <c r="E8" s="192" t="s">
+      <c r="C8" s="184"/>
+      <c r="D8" s="185"/>
+      <c r="E8" s="183" t="s">
         <v>132</v>
       </c>
-      <c r="F8" s="193"/>
-      <c r="G8" s="189"/>
-      <c r="H8" s="189"/>
-      <c r="I8" s="189"/>
-      <c r="J8" s="189"/>
+      <c r="F8" s="185"/>
+      <c r="G8" s="178"/>
+      <c r="H8" s="178"/>
+      <c r="I8" s="178"/>
+      <c r="J8" s="178"/>
       <c r="K8" s="26"/>
     </row>
     <row r="9" spans="1:13" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A9" s="126">
         <v>4</v>
       </c>
-      <c r="B9" s="192" t="s">
+      <c r="B9" s="183" t="s">
         <v>133</v>
       </c>
-      <c r="C9" s="195"/>
-      <c r="D9" s="193"/>
-      <c r="E9" s="192" t="s">
+      <c r="C9" s="184"/>
+      <c r="D9" s="185"/>
+      <c r="E9" s="183" t="s">
         <v>132</v>
       </c>
-      <c r="F9" s="193"/>
-      <c r="G9" s="196"/>
-      <c r="H9" s="189"/>
-      <c r="I9" s="189"/>
-      <c r="J9" s="189"/>
+      <c r="F9" s="185"/>
+      <c r="G9" s="179"/>
+      <c r="H9" s="178"/>
+      <c r="I9" s="178"/>
+      <c r="J9" s="178"/>
       <c r="K9" s="26"/>
     </row>
     <row r="10" spans="1:13" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A10" s="126">
         <v>5</v>
       </c>
-      <c r="B10" s="192" t="s">
+      <c r="B10" s="183" t="s">
         <v>131</v>
       </c>
-      <c r="C10" s="195"/>
-      <c r="D10" s="193"/>
-      <c r="E10" s="192" t="s">
+      <c r="C10" s="184"/>
+      <c r="D10" s="185"/>
+      <c r="E10" s="183" t="s">
         <v>129</v>
       </c>
-      <c r="F10" s="193"/>
-      <c r="G10" s="189"/>
-      <c r="H10" s="189"/>
-      <c r="I10" s="189"/>
-      <c r="J10" s="189"/>
+      <c r="F10" s="185"/>
+      <c r="G10" s="178"/>
+      <c r="H10" s="178"/>
+      <c r="I10" s="178"/>
+      <c r="J10" s="178"/>
       <c r="K10" s="26"/>
     </row>
     <row r="11" spans="1:13" ht="18" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="126">
         <v>6</v>
       </c>
-      <c r="B11" s="200" t="s">
+      <c r="B11" s="186" t="s">
         <v>130</v>
       </c>
-      <c r="C11" s="201"/>
-      <c r="D11" s="202"/>
-      <c r="E11" s="192" t="s">
+      <c r="C11" s="187"/>
+      <c r="D11" s="188"/>
+      <c r="E11" s="183" t="s">
         <v>129</v>
       </c>
-      <c r="F11" s="193"/>
-      <c r="G11" s="197"/>
-      <c r="H11" s="198"/>
-      <c r="I11" s="198"/>
-      <c r="J11" s="199"/>
+      <c r="F11" s="185"/>
+      <c r="G11" s="180"/>
+      <c r="H11" s="181"/>
+      <c r="I11" s="181"/>
+      <c r="J11" s="182"/>
     </row>
     <row r="12" spans="1:13" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A12" s="23"/>
@@ -9657,6 +9657,17 @@
     </row>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="A1:J2"/>
+    <mergeCell ref="A4:J4"/>
+    <mergeCell ref="G5:J5"/>
+    <mergeCell ref="G6:J6"/>
+    <mergeCell ref="G7:J7"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="B5:D5"/>
     <mergeCell ref="G8:J8"/>
     <mergeCell ref="G9:J9"/>
     <mergeCell ref="G10:J10"/>
@@ -9669,17 +9680,6 @@
     <mergeCell ref="E11:F11"/>
     <mergeCell ref="B8:D8"/>
     <mergeCell ref="B9:D9"/>
-    <mergeCell ref="A1:J2"/>
-    <mergeCell ref="A4:J4"/>
-    <mergeCell ref="G5:J5"/>
-    <mergeCell ref="G6:J6"/>
-    <mergeCell ref="G7:J7"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="B5:D5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -9691,106 +9691,106 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:9" ht="18" x14ac:dyDescent="0.3">
-      <c r="A1" s="207" t="s">
+      <c r="A1" s="203" t="s">
         <v>147</v>
       </c>
-      <c r="B1" s="208"/>
-      <c r="C1" s="208"/>
-      <c r="D1" s="208"/>
-      <c r="E1" s="208"/>
-      <c r="F1" s="208"/>
-      <c r="G1" s="208"/>
-      <c r="H1" s="208"/>
+      <c r="B1" s="204"/>
+      <c r="C1" s="204"/>
+      <c r="D1" s="204"/>
+      <c r="E1" s="204"/>
+      <c r="F1" s="204"/>
+      <c r="G1" s="204"/>
+      <c r="H1" s="204"/>
     </row>
     <row r="2" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="3" spans="1:9" ht="19.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="203" t="s">
+      <c r="A3" s="211" t="s">
         <v>97</v>
       </c>
-      <c r="B3" s="204"/>
-      <c r="C3" s="204"/>
-      <c r="D3" s="204"/>
-      <c r="E3" s="204"/>
-      <c r="F3" s="204"/>
-      <c r="G3" s="204"/>
-      <c r="H3" s="204"/>
+      <c r="B3" s="212"/>
+      <c r="C3" s="212"/>
+      <c r="D3" s="212"/>
+      <c r="E3" s="212"/>
+      <c r="F3" s="212"/>
+      <c r="G3" s="212"/>
+      <c r="H3" s="212"/>
       <c r="I3" s="26"/>
     </row>
     <row r="4" spans="1:9" ht="19.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="133" t="s">
         <v>140</v>
       </c>
-      <c r="B4" s="209" t="s">
+      <c r="B4" s="205" t="s">
         <v>146</v>
       </c>
-      <c r="C4" s="210"/>
-      <c r="D4" s="210"/>
-      <c r="E4" s="210"/>
-      <c r="F4" s="211"/>
-      <c r="G4" s="205" t="s">
+      <c r="C4" s="206"/>
+      <c r="D4" s="206"/>
+      <c r="E4" s="206"/>
+      <c r="F4" s="207"/>
+      <c r="G4" s="213" t="s">
         <v>145</v>
       </c>
-      <c r="H4" s="206"/>
+      <c r="H4" s="214"/>
       <c r="I4" s="26"/>
     </row>
     <row r="5" spans="1:9" ht="18" thickTop="1" x14ac:dyDescent="0.35">
       <c r="A5" s="134">
         <v>1</v>
       </c>
-      <c r="B5" s="212" t="s">
+      <c r="B5" s="208" t="s">
         <v>144</v>
       </c>
-      <c r="C5" s="213"/>
-      <c r="D5" s="213"/>
-      <c r="E5" s="213"/>
-      <c r="F5" s="214"/>
-      <c r="G5" s="155"/>
-      <c r="H5" s="157"/>
+      <c r="C5" s="209"/>
+      <c r="D5" s="209"/>
+      <c r="E5" s="209"/>
+      <c r="F5" s="210"/>
+      <c r="G5" s="165"/>
+      <c r="H5" s="167"/>
       <c r="I5" s="26"/>
     </row>
     <row r="6" spans="1:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="A6" s="132">
         <v>2</v>
       </c>
-      <c r="B6" s="172" t="s">
+      <c r="B6" s="155" t="s">
         <v>143</v>
       </c>
-      <c r="C6" s="173"/>
-      <c r="D6" s="173"/>
-      <c r="E6" s="173"/>
-      <c r="F6" s="174"/>
-      <c r="G6" s="159"/>
-      <c r="H6" s="159"/>
+      <c r="C6" s="156"/>
+      <c r="D6" s="156"/>
+      <c r="E6" s="156"/>
+      <c r="F6" s="157"/>
+      <c r="G6" s="169"/>
+      <c r="H6" s="169"/>
       <c r="I6" s="26"/>
     </row>
     <row r="7" spans="1:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="A7" s="132">
         <v>3</v>
       </c>
-      <c r="B7" s="172" t="s">
+      <c r="B7" s="155" t="s">
         <v>142</v>
       </c>
-      <c r="C7" s="173"/>
-      <c r="D7" s="173"/>
-      <c r="E7" s="173"/>
-      <c r="F7" s="174"/>
-      <c r="G7" s="158"/>
-      <c r="H7" s="160"/>
+      <c r="C7" s="156"/>
+      <c r="D7" s="156"/>
+      <c r="E7" s="156"/>
+      <c r="F7" s="157"/>
+      <c r="G7" s="168"/>
+      <c r="H7" s="170"/>
       <c r="I7" s="26"/>
     </row>
     <row r="8" spans="1:9" ht="18" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A8" s="132">
         <v>4</v>
       </c>
-      <c r="B8" s="175" t="s">
+      <c r="B8" s="158" t="s">
         <v>141</v>
       </c>
-      <c r="C8" s="176"/>
-      <c r="D8" s="176"/>
-      <c r="E8" s="176"/>
-      <c r="F8" s="177"/>
-      <c r="G8" s="161"/>
-      <c r="H8" s="163"/>
+      <c r="C8" s="159"/>
+      <c r="D8" s="159"/>
+      <c r="E8" s="159"/>
+      <c r="F8" s="160"/>
+      <c r="G8" s="171"/>
+      <c r="H8" s="173"/>
       <c r="I8" s="26"/>
     </row>
     <row r="9" spans="1:9" ht="15" thickTop="1" x14ac:dyDescent="0.3">
@@ -9798,11 +9798,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="B5:F5"/>
-    <mergeCell ref="B6:F6"/>
-    <mergeCell ref="B7:F7"/>
     <mergeCell ref="B8:F8"/>
     <mergeCell ref="A3:H3"/>
     <mergeCell ref="G4:H4"/>
@@ -9810,6 +9805,11 @@
     <mergeCell ref="G6:H6"/>
     <mergeCell ref="G7:H7"/>
     <mergeCell ref="G8:H8"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="B5:F5"/>
+    <mergeCell ref="B6:F6"/>
+    <mergeCell ref="B7:F7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
